--- a/src/Archivos/Nominas/Pruebas.xlsx
+++ b/src/Archivos/Nominas/Pruebas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soporte\Documents\Proyectos web\Proyectos JavaScript\CorreosNominas\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soporte\Documents\Proyectos web\Proyectos JavaScript\SIGG\src\Archivos\Nominas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192A1C4E-B075-4E0A-BE4D-B429D2BBDF98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A3C88CF-A01A-4F9B-AE72-D49C303CC4A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A91ABAD6-1B15-4688-9B87-0A56E9438503}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{A91ABAD6-1B15-4688-9B87-0A56E9438503}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>Nombre</t>
   </si>
@@ -63,6 +63,42 @@
   </si>
   <si>
     <t>soporte@gemak.com.mx</t>
+  </si>
+  <si>
+    <t>Curp</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>Nomina</t>
+  </si>
+  <si>
+    <t>A132</t>
+  </si>
+  <si>
+    <t>A456</t>
+  </si>
+  <si>
+    <t>A789</t>
+  </si>
+  <si>
+    <t>A258</t>
+  </si>
+  <si>
+    <t>Planta</t>
+  </si>
+  <si>
+    <t>Morelos</t>
   </si>
 </sst>
 </file>
@@ -443,108 +479,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A11A3C-933D-43E2-88DA-DB26B706DDCC}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="64.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
